--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/pre LAM_HRM-2031-0292/Panel 02/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -460,19 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.56137</v>
+        <v>17.03861</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63223</v>
+        <v>16.557</v>
       </c>
       <c r="E2" t="n">
-        <v>16.72385</v>
+        <v>16.79844</v>
+      </c>
+      <c r="F2" t="n">
+        <v>42.73815</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05002</v>
+        <v>0.05092</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8298</v>
+        <v>1.80586</v>
       </c>
     </row>
     <row r="3">
@@ -482,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.96495</v>
+        <v>16.95714</v>
       </c>
       <c r="D3" t="n">
-        <v>16.30312</v>
+        <v>16.70602</v>
       </c>
       <c r="E3" t="n">
-        <v>16.66632</v>
+        <v>16.77604</v>
       </c>
       <c r="F3" t="n">
-        <v>41.73583</v>
+        <v>42.69807</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.05101</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80726</v>
+        <v>1.82289</v>
       </c>
     </row>
     <row r="4">
@@ -506,25 +509,23 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16.90167</v>
       </c>
       <c r="D4" t="n">
-        <v>16.64532</v>
+        <v>16.4973</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74257</v>
+        <v>16.89777</v>
       </c>
       <c r="F4" t="n">
-        <v>42.39667</v>
+        <v>42.11383</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05073</v>
+        <v>0.05051</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80416</v>
+        <v>1.79235</v>
       </c>
     </row>
     <row r="5">
@@ -533,25 +534,23 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
+      <c r="C5" t="n">
+        <v>17.03559</v>
       </c>
       <c r="D5" t="n">
-        <v>16.57164</v>
+        <v>16.44344</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54866</v>
+        <v>16.57548</v>
       </c>
       <c r="F5" t="n">
-        <v>42.43444</v>
+        <v>42.85848</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05008</v>
+        <v>0.0504</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81459</v>
+        <v>1.82435</v>
       </c>
     </row>
     <row r="6">
@@ -561,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.87945</v>
+        <v>16.74807</v>
       </c>
       <c r="D6" t="n">
-        <v>16.58444</v>
+        <v>16.37529</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63035</v>
+        <v>16.53619</v>
       </c>
       <c r="F6" t="n">
-        <v>42.59647</v>
+        <v>42.08358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05065</v>
-      </c>
-      <c r="H6" t="e">
-        <v>#DIV/0!</v>
+        <v>0.05103</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.85183</v>
       </c>
     </row>
     <row r="7">
@@ -586,24 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.82776</v>
+        <v>16.81784</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54524</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 16.48 </t>
-        </is>
+        <v>16.52223</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.69278</v>
       </c>
       <c r="F7" t="n">
-        <v>42.09205</v>
+        <v>43.16976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0509</v>
+        <v>0.04973</v>
       </c>
       <c r="H7" t="n">
-        <v>1.84472</v>
+        <v>1.84092</v>
       </c>
     </row>
     <row r="8">
@@ -613,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.58413</v>
+        <v>16.73844</v>
       </c>
       <c r="D8" t="n">
-        <v>16.29018</v>
+        <v>16.57012</v>
       </c>
       <c r="E8" t="n">
-        <v>16.57032</v>
+        <v>16.66167</v>
       </c>
       <c r="F8" t="n">
-        <v>43.47676</v>
+        <v>42.72932</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05053</v>
+        <v>0.04981</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81121</v>
+        <v>1.82911</v>
       </c>
     </row>
     <row r="9">
@@ -638,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.5722</v>
+        <v>16.82367</v>
       </c>
       <c r="D9" t="n">
-        <v>16.46701</v>
+        <v>16.39446</v>
       </c>
       <c r="E9" t="n">
-        <v>16.57513</v>
+        <v>16.56499</v>
       </c>
       <c r="F9" t="n">
-        <v>42.1678</v>
+        <v>41.91079</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05138</v>
+        <v>0.05063</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82453</v>
+        <v>1.83127</v>
       </c>
     </row>
     <row r="10">
@@ -663,33 +660,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.92611</v>
+        <v>16.84068</v>
       </c>
       <c r="D10" t="n">
-        <v>16.55051</v>
+        <v>16.59939</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61842</v>
+        <v>16.76228</v>
       </c>
       <c r="F10" t="n">
-        <v>42.03215</v>
+        <v>42.14121</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05053</v>
+        <v>0.05105</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81221</v>
+        <v>1.83087</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -701,14 +713,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.12113</v>
+          <t>Trace 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -717,12 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.124</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,12 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.13224</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -743,12 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.11465</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -756,12 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.1255</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -769,12 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.09648</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -782,12 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.09399</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -795,12 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.11841</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -808,12 +772,6 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.09992</v>
-      </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
@@ -869,28 +827,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7559</v>
+        <v>0.72914</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08047</v>
+        <v>0.08087</v>
       </c>
       <c r="E22" t="n">
-        <v>0.60375</v>
+        <v>0.60232</v>
       </c>
       <c r="F22" t="n">
-        <v>0.95327</v>
+        <v>0.95389</v>
       </c>
       <c r="G22" t="n">
-        <v>0.11078</v>
+        <v>0.10955</v>
       </c>
       <c r="H22" t="n">
-        <v>0.00763</v>
+        <v>0.00747</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09186</v>
+        <v>0.09632</v>
       </c>
       <c r="J22" t="n">
-        <v>0.12925</v>
+        <v>0.12623</v>
       </c>
     </row>
     <row r="23">
@@ -900,28 +858,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75632</v>
+        <v>0.75568</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08008</v>
+        <v>0.08286</v>
       </c>
       <c r="E23" t="n">
-        <v>0.61805</v>
+        <v>0.59663</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9752</v>
+        <v>0.95897</v>
       </c>
       <c r="G23" t="n">
-        <v>0.10898</v>
+        <v>0.10807</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00746</v>
+        <v>0.00777</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09208</v>
+        <v>0.09368</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1251</v>
+        <v>0.12656</v>
       </c>
     </row>
     <row r="24">
@@ -931,28 +889,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75805</v>
+        <v>0.76237</v>
       </c>
       <c r="D24" t="n">
-        <v>0.082</v>
+        <v>0.07982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.60114</v>
+        <v>0.59946</v>
       </c>
       <c r="F24" t="n">
-        <v>0.94817</v>
+        <v>0.96512</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10833</v>
+        <v>0.10915</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00763</v>
+        <v>0.00768</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09241000000000001</v>
+        <v>0.09344</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12777</v>
+        <v>0.12522</v>
       </c>
     </row>
     <row r="25">
@@ -962,28 +920,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.74662</v>
+        <v>0.74779</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08408</v>
+        <v>0.08024000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60871</v>
+        <v>0.5989</v>
       </c>
       <c r="F25" t="n">
-        <v>0.97903</v>
+        <v>0.9811800000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1099</v>
+        <v>0.10783</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00772</v>
+        <v>0.00756</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09292</v>
+        <v>0.09331</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12743</v>
+        <v>0.12413</v>
       </c>
     </row>
     <row r="26">
@@ -993,28 +951,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75229</v>
+        <v>0.74159</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08116</v>
+        <v>0.08187</v>
       </c>
       <c r="E26" t="n">
-        <v>0.61013</v>
+        <v>0.60395</v>
       </c>
       <c r="F26" t="n">
-        <v>0.96518</v>
+        <v>0.97126</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10939</v>
+        <v>0.11057</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00756</v>
+        <v>0.00768</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09265</v>
+        <v>0.09356</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12617</v>
+        <v>0.12619</v>
       </c>
     </row>
     <row r="27">
@@ -1024,28 +982,28 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.7526</v>
+        <v>0.74688</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07939</v>
+        <v>0.08161</v>
       </c>
       <c r="E27" t="n">
-        <v>0.60572</v>
+        <v>0.61127</v>
       </c>
       <c r="F27" t="n">
-        <v>0.95599</v>
+        <v>0.96944</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10872</v>
+        <v>0.10832</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00773</v>
+        <v>0.00765</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09485</v>
+        <v>0.09358</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12877</v>
+        <v>0.12759</v>
       </c>
     </row>
     <row r="28">
@@ -1055,28 +1013,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.74444</v>
+        <v>0.7471</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08221000000000001</v>
+        <v>0.08044</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6031300000000001</v>
+        <v>0.58792</v>
       </c>
       <c r="F28" t="n">
-        <v>0.95304</v>
+        <v>0.96449</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11029</v>
+        <v>0.11099</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0076</v>
+        <v>0.00761</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0936</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12505</v>
+        <v>0.12858</v>
       </c>
     </row>
     <row r="29">
@@ -1086,28 +1044,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.74413</v>
+        <v>0.75468</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08212999999999999</v>
+        <v>0.08008999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60828</v>
+        <v>0.60854</v>
       </c>
       <c r="F29" t="n">
-        <v>0.95513</v>
+        <v>0.97201</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10851</v>
+        <v>0.1092</v>
       </c>
       <c r="H29" t="n">
         <v>0.00767</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09258</v>
+        <v>0.09440999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12627</v>
+        <v>0.12642</v>
       </c>
     </row>
     <row r="30">
@@ -1117,28 +1075,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7508899999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08169</v>
+        <v>0.08044</v>
       </c>
       <c r="E30" t="n">
-        <v>0.61169</v>
+        <v>0.6026899999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9593699999999999</v>
+        <v>0.9738</v>
       </c>
       <c r="G30" t="n">
-        <v>0.10836</v>
+        <v>0.10961</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00766</v>
+        <v>0.00752</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09361</v>
+        <v>0.09404999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1263</v>
+        <v>0.13032</v>
       </c>
     </row>
   </sheetData>
